--- a/artfynd/A 3426-2026 artfynd.xlsx
+++ b/artfynd/A 3426-2026 artfynd.xlsx
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133039517</v>
+        <v>133039508</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619589</v>
+        <v>619657</v>
       </c>
       <c r="R2" t="n">
-        <v>7013257</v>
+        <v>7013205</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +776,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133041159</v>
+        <v>133039517</v>
       </c>
       <c r="B3" t="n">
         <v>57955</v>
@@ -823,23 +828,23 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619667</v>
+        <v>619589</v>
       </c>
       <c r="R3" t="n">
-        <v>7013333</v>
+        <v>7013257</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,72 +898,68 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133039508</v>
+        <v>133041159</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619657</v>
+        <v>619667</v>
       </c>
       <c r="R4" t="n">
-        <v>7013205</v>
+        <v>7013333</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,70 +1007,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133039512</v>
+        <v>133039525</v>
       </c>
       <c r="B5" t="n">
-        <v>92378</v>
+        <v>91881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619598</v>
+        <v>619539</v>
       </c>
       <c r="R5" t="n">
-        <v>7013213</v>
+        <v>7013311</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,12 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bilden visar rynkskinn, rosenticka och ullticka på en granlåga.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1114,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,48 +1132,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133039525</v>
+        <v>133039512</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>92378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619539</v>
+        <v>619598</v>
       </c>
       <c r="R6" t="n">
-        <v>7013311</v>
+        <v>7013213</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1215,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bilden visar rynkskinn, rosenticka och ullticka på en granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,6 +1229,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1355,7 +1355,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133039495</v>
+        <v>133039492</v>
       </c>
       <c r="B8" t="n">
         <v>57955</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619649</v>
+        <v>619666</v>
       </c>
       <c r="R8" t="n">
-        <v>7013130</v>
+        <v>7013114</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,7 +1470,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133039492</v>
+        <v>133039495</v>
       </c>
       <c r="B9" t="n">
         <v>57955</v>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619666</v>
+        <v>619649</v>
       </c>
       <c r="R9" t="n">
-        <v>7013114</v>
+        <v>7013130</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2030,48 +2030,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133041136</v>
+        <v>133039538</v>
       </c>
       <c r="B14" t="n">
-        <v>92217</v>
+        <v>92378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>619609</v>
+        <v>619707</v>
       </c>
       <c r="R14" t="n">
-        <v>7013215</v>
+        <v>7013337</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,12 +2125,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2244,48 +2244,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133039538</v>
+        <v>133041136</v>
       </c>
       <c r="B16" t="n">
-        <v>92378</v>
+        <v>92217</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>619707</v>
+        <v>619609</v>
       </c>
       <c r="R16" t="n">
-        <v>7013337</v>
+        <v>7013215</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,12 +2339,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2565,48 +2565,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133041146</v>
+        <v>133039545</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619516</v>
+        <v>619835</v>
       </c>
       <c r="R19" t="n">
-        <v>7013311</v>
+        <v>7013242</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,12 +2660,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2779,48 +2779,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133039545</v>
+        <v>133041146</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>619835</v>
+        <v>619516</v>
       </c>
       <c r="R21" t="n">
-        <v>7013242</v>
+        <v>7013311</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,22 +2874,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133039539</v>
+        <v>133039522</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,21 +2897,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2921,10 +2921,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619802</v>
+        <v>619546</v>
       </c>
       <c r="R22" t="n">
-        <v>7013343</v>
+        <v>7013304</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2993,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133039522</v>
+        <v>133039539</v>
       </c>
       <c r="B23" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,21 +3004,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619546</v>
+        <v>619802</v>
       </c>
       <c r="R23" t="n">
-        <v>7013304</v>
+        <v>7013343</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3677,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133039529</v>
+        <v>133041170</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3688,37 +3688,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619498</v>
+        <v>619669</v>
       </c>
       <c r="R29" t="n">
-        <v>7013345</v>
+        <v>7013158</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3747,7 +3755,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3757,7 +3765,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3772,19 +3780,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133039521</v>
+        <v>133039529</v>
       </c>
       <c r="B30" t="n">
         <v>79333</v>
@@ -3819,13 +3827,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>619582</v>
+        <v>619498</v>
       </c>
       <c r="R30" t="n">
-        <v>7013292</v>
+        <v>7013345</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3854,7 +3862,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3864,7 +3872,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3891,7 +3899,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133039496</v>
+        <v>133039521</v>
       </c>
       <c r="B31" t="n">
         <v>79333</v>
@@ -3920,22 +3928,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>619651</v>
+        <v>619582</v>
       </c>
       <c r="R31" t="n">
-        <v>7013134</v>
+        <v>7013292</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3964,7 +3969,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3974,7 +3979,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,7 +3988,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4002,48 +4006,51 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133041154</v>
+        <v>133039496</v>
       </c>
       <c r="B32" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>619554</v>
+        <v>619651</v>
       </c>
       <c r="R32" t="n">
-        <v>7013316</v>
+        <v>7013134</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4072,7 +4079,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4082,7 +4089,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4091,18 +4098,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4216,56 +4224,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133041170</v>
+        <v>133041154</v>
       </c>
       <c r="B34" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>619669</v>
+        <v>619554</v>
       </c>
       <c r="R34" t="n">
-        <v>7013158</v>
+        <v>7013316</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4331,10 +4331,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133041148</v>
+        <v>133039511</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4342,40 +4342,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>619495</v>
+        <v>619605</v>
       </c>
       <c r="R35" t="n">
-        <v>7013342</v>
+        <v>7013212</v>
       </c>
       <c r="S35" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4404,7 +4401,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4414,7 +4411,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4423,19 +4420,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4549,10 +4545,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133039511</v>
+        <v>133041148</v>
       </c>
       <c r="B37" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4560,37 +4556,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>619605</v>
+        <v>619495</v>
       </c>
       <c r="R37" t="n">
-        <v>7013212</v>
+        <v>7013342</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4619,7 +4618,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4629,7 +4628,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4638,18 +4637,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4763,45 +4763,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133039510</v>
+        <v>133039520</v>
       </c>
       <c r="B39" t="n">
-        <v>92217</v>
+        <v>99130</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>619605</v>
+        <v>619585</v>
       </c>
       <c r="R39" t="n">
-        <v>7013212</v>
+        <v>7013257</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4833,7 +4845,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4843,7 +4855,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4852,6 +4864,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4870,48 +4883,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133039534</v>
+        <v>133041161</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>97995</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>619647</v>
+        <v>619696</v>
       </c>
       <c r="R40" t="n">
-        <v>7013315</v>
+        <v>7013344</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4940,7 +4953,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4950,7 +4963,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4965,69 +4978,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133039520</v>
+        <v>133039510</v>
       </c>
       <c r="B41" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>619585</v>
+        <v>619605</v>
       </c>
       <c r="R41" t="n">
-        <v>7013257</v>
+        <v>7013212</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -5059,7 +5060,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5069,7 +5070,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5078,7 +5079,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5097,48 +5097,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133041161</v>
+        <v>133039534</v>
       </c>
       <c r="B42" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>619696</v>
+        <v>619647</v>
       </c>
       <c r="R42" t="n">
-        <v>7013344</v>
+        <v>7013315</v>
       </c>
       <c r="S42" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5192,60 +5192,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133041147</v>
+        <v>133039519</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>619523</v>
+        <v>619592</v>
       </c>
       <c r="R43" t="n">
-        <v>7013308</v>
+        <v>7013241</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5299,44 +5299,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133039537</v>
+        <v>133039535</v>
       </c>
       <c r="B44" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>619664</v>
+        <v>619667</v>
       </c>
       <c r="R44" t="n">
-        <v>7013327</v>
+        <v>7013336</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,7 +5418,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133039519</v>
+        <v>133039507</v>
       </c>
       <c r="B45" t="n">
         <v>91881</v>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>619592</v>
+        <v>619673</v>
       </c>
       <c r="R45" t="n">
-        <v>7013241</v>
+        <v>7013196</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5525,48 +5525,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133039535</v>
+        <v>133041147</v>
       </c>
       <c r="B46" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>619667</v>
+        <v>619523</v>
       </c>
       <c r="R46" t="n">
-        <v>7013336</v>
+        <v>7013308</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5620,19 +5620,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133039507</v>
+        <v>133041143</v>
       </c>
       <c r="B47" t="n">
         <v>91881</v>
@@ -5663,17 +5663,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>619673</v>
+        <v>619558</v>
       </c>
       <c r="R47" t="n">
-        <v>7013196</v>
+        <v>7013293</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5727,60 +5727,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133041143</v>
+        <v>133039537</v>
       </c>
       <c r="B48" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>619558</v>
+        <v>619664</v>
       </c>
       <c r="R48" t="n">
-        <v>7013293</v>
+        <v>7013327</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5834,12 +5834,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133039530</v>
+        <v>133041130</v>
       </c>
       <c r="B50" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5964,40 +5964,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>619558</v>
+        <v>619658</v>
       </c>
       <c r="R50" t="n">
-        <v>7013324</v>
+        <v>7013169</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6026,7 +6023,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6036,7 +6033,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6045,67 +6042,74 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133039514</v>
+        <v>133041138</v>
       </c>
       <c r="B51" t="n">
-        <v>97995</v>
+        <v>57955</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>619610</v>
+        <v>619593</v>
       </c>
       <c r="R51" t="n">
-        <v>7013231</v>
+        <v>7013220</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6134,7 +6138,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6144,7 +6148,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6159,60 +6163,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133041130</v>
+        <v>133039514</v>
       </c>
       <c r="B52" t="n">
-        <v>79333</v>
+        <v>97995</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>619658</v>
+        <v>619610</v>
       </c>
       <c r="R52" t="n">
-        <v>7013169</v>
+        <v>7013231</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6241,7 +6245,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6251,7 +6255,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6266,22 +6270,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133041138</v>
+        <v>133039530</v>
       </c>
       <c r="B53" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6289,45 +6293,40 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>619593</v>
+        <v>619558</v>
       </c>
       <c r="R53" t="n">
-        <v>7013220</v>
+        <v>7013324</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6356,7 +6355,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6366,7 +6365,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6375,18 +6374,19 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133041139</v>
+        <v>133039540</v>
       </c>
       <c r="B58" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6845,37 +6845,45 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>619607</v>
+        <v>619839</v>
       </c>
       <c r="R58" t="n">
-        <v>7013209</v>
+        <v>7013377</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6904,7 +6912,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6914,7 +6922,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6929,12 +6942,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7048,10 +7061,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133039540</v>
+        <v>133041139</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7059,45 +7072,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>619839</v>
+        <v>619607</v>
       </c>
       <c r="R60" t="n">
-        <v>7013377</v>
+        <v>7013209</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7126,7 +7131,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7136,12 +7141,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7156,12 +7156,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7510,10 +7510,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133041135</v>
+        <v>133039506</v>
       </c>
       <c r="B64" t="n">
-        <v>56522</v>
+        <v>91918</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7521,45 +7521,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>619690</v>
+        <v>619674</v>
       </c>
       <c r="R64" t="n">
         <v>7013194</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7588,7 +7580,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7598,7 +7590,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7613,22 +7605,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133039506</v>
+        <v>133039505</v>
       </c>
       <c r="B65" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7636,21 +7628,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7660,10 +7652,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>619674</v>
+        <v>619683</v>
       </c>
       <c r="R65" t="n">
-        <v>7013194</v>
+        <v>7013204</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7695,7 +7687,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7705,7 +7697,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7732,32 +7724,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133039502</v>
+        <v>133039504</v>
       </c>
       <c r="B66" t="n">
-        <v>91932</v>
+        <v>91881</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7767,13 +7759,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>619662</v>
+        <v>619679</v>
       </c>
       <c r="R66" t="n">
-        <v>7013170</v>
+        <v>7013155</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7802,7 +7794,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7812,7 +7804,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7839,48 +7831,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133039494</v>
+        <v>133039547</v>
       </c>
       <c r="B67" t="n">
-        <v>92217</v>
+        <v>92378</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>619655</v>
+        <v>619754</v>
       </c>
       <c r="R67" t="n">
-        <v>7013115</v>
+        <v>7013242</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7912,7 +7901,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7922,7 +7911,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7931,7 +7920,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7950,32 +7938,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133039547</v>
+        <v>133039542</v>
       </c>
       <c r="B68" t="n">
-        <v>92378</v>
+        <v>79333</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7985,10 +7973,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>619754</v>
+        <v>619802</v>
       </c>
       <c r="R68" t="n">
-        <v>7013242</v>
+        <v>7013443</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -8020,7 +8008,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8030,7 +8018,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8057,10 +8045,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133039505</v>
+        <v>133039494</v>
       </c>
       <c r="B69" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8068,37 +8056,40 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>619683</v>
+        <v>619655</v>
       </c>
       <c r="R69" t="n">
-        <v>7013204</v>
+        <v>7013115</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8127,7 +8118,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8137,7 +8128,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8146,6 +8137,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8164,10 +8156,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133039548</v>
+        <v>133039502</v>
       </c>
       <c r="B70" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8175,37 +8167,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>619671</v>
+        <v>619662</v>
       </c>
       <c r="R70" t="n">
-        <v>7013153</v>
+        <v>7013170</v>
       </c>
       <c r="S70" t="n">
         <v>3</v>
@@ -8237,7 +8226,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8247,12 +8236,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Växandes på gammal sälg</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8261,24 +8245,8 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8295,48 +8263,51 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133039504</v>
+        <v>133039548</v>
       </c>
       <c r="B71" t="n">
-        <v>91881</v>
+        <v>80438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>619679</v>
+        <v>619671</v>
       </c>
       <c r="R71" t="n">
-        <v>7013155</v>
+        <v>7013153</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8365,7 +8336,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8375,7 +8346,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Växandes på gammal sälg</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8384,8 +8360,24 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8509,7 +8501,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133039542</v>
+        <v>133039491</v>
       </c>
       <c r="B73" t="n">
         <v>79333</v>
@@ -8544,10 +8536,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>619802</v>
+        <v>619664</v>
       </c>
       <c r="R73" t="n">
-        <v>7013443</v>
+        <v>7013113</v>
       </c>
       <c r="S73" t="n">
         <v>3</v>
@@ -8579,7 +8571,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8589,7 +8581,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8616,10 +8608,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133039491</v>
+        <v>133041135</v>
       </c>
       <c r="B74" t="n">
-        <v>79333</v>
+        <v>56522</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8627,37 +8619,45 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>619664</v>
+        <v>619690</v>
       </c>
       <c r="R74" t="n">
-        <v>7013113</v>
+        <v>7013194</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8711,12 +8711,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133039532</v>
+        <v>133039527</v>
       </c>
       <c r="B80" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9290,37 +9290,40 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>619594</v>
+        <v>619516</v>
       </c>
       <c r="R80" t="n">
-        <v>7013273</v>
+        <v>7013323</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9349,7 +9352,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9359,7 +9362,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9368,6 +9371,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9386,10 +9390,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133039527</v>
+        <v>133039532</v>
       </c>
       <c r="B81" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9397,40 +9401,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>619516</v>
+        <v>619594</v>
       </c>
       <c r="R81" t="n">
-        <v>7013323</v>
+        <v>7013273</v>
       </c>
       <c r="S81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9459,7 +9460,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9469,7 +9470,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9478,7 +9479,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3426-2026 artfynd.xlsx
+++ b/artfynd/A 3426-2026 artfynd.xlsx
@@ -675,46 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133039508</v>
+        <v>133039517</v>
       </c>
       <c r="B2" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619657</v>
+        <v>619589</v>
       </c>
       <c r="R2" t="n">
-        <v>7013205</v>
+        <v>7013257</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,7 +772,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133039517</v>
+        <v>133041159</v>
       </c>
       <c r="B3" t="n">
         <v>57955</v>
@@ -828,23 +823,23 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619589</v>
+        <v>619667</v>
       </c>
       <c r="R3" t="n">
-        <v>7013257</v>
+        <v>7013333</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,68 +893,72 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133041159</v>
+        <v>133039508</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619667</v>
+        <v>619657</v>
       </c>
       <c r="R4" t="n">
-        <v>7013333</v>
+        <v>7013205</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,18 +1006,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133039492</v>
+        <v>133039495</v>
       </c>
       <c r="B8" t="n">
         <v>57955</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619666</v>
+        <v>619649</v>
       </c>
       <c r="R8" t="n">
-        <v>7013114</v>
+        <v>7013130</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,7 +1470,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133039495</v>
+        <v>133039492</v>
       </c>
       <c r="B9" t="n">
         <v>57955</v>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619649</v>
+        <v>619666</v>
       </c>
       <c r="R9" t="n">
-        <v>7013130</v>
+        <v>7013114</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1700,53 +1700,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133039543</v>
+        <v>133039533</v>
       </c>
       <c r="B11" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619864</v>
+        <v>619679</v>
       </c>
       <c r="R11" t="n">
-        <v>7013328</v>
+        <v>7013284</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1778,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,7 +1789,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1816,45 +1807,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133039533</v>
+        <v>133039543</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619679</v>
+        <v>619864</v>
       </c>
       <c r="R12" t="n">
-        <v>7013284</v>
+        <v>7013328</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1886,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1896,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,6 +1904,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3327,42 +3327,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133039541</v>
+        <v>133039550</v>
       </c>
       <c r="B26" t="n">
-        <v>57136</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3370,10 +3374,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619819</v>
+        <v>619673</v>
       </c>
       <c r="R26" t="n">
-        <v>7013478</v>
+        <v>7013115</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3405,7 +3409,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3419,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3424,6 +3428,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3435,14 +3440,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133039536</v>
+        <v>133039541</v>
       </c>
       <c r="B27" t="n">
         <v>57136</v>
@@ -3475,7 +3480,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3485,10 +3490,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>619674</v>
+        <v>619819</v>
       </c>
       <c r="R27" t="n">
-        <v>7013329</v>
+        <v>7013478</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3520,7 +3525,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3530,7 +3535,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3557,46 +3562,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133039550</v>
+        <v>133039536</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>57136</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3604,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619673</v>
+        <v>619674</v>
       </c>
       <c r="R28" t="n">
-        <v>7013115</v>
+        <v>7013329</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3639,7 +3640,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3649,7 +3650,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3658,7 +3659,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133039511</v>
+        <v>133041148</v>
       </c>
       <c r="B35" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4342,37 +4342,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>619605</v>
+        <v>619495</v>
       </c>
       <c r="R35" t="n">
-        <v>7013212</v>
+        <v>7013342</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4401,7 +4404,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4411,7 +4414,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4420,28 +4423,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133041133</v>
+        <v>133039511</v>
       </c>
       <c r="B36" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4449,37 +4453,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>619696</v>
+        <v>619605</v>
       </c>
       <c r="R36" t="n">
-        <v>7013181</v>
+        <v>7013212</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4508,7 +4512,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4518,7 +4522,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4533,22 +4537,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133041148</v>
+        <v>133041133</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4556,40 +4560,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>619495</v>
+        <v>619696</v>
       </c>
       <c r="R37" t="n">
-        <v>7013342</v>
+        <v>7013181</v>
       </c>
       <c r="S37" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4618,7 +4619,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4628,7 +4629,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4637,7 +4638,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4883,48 +4883,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133041161</v>
+        <v>133039510</v>
       </c>
       <c r="B40" t="n">
-        <v>97995</v>
+        <v>92217</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>619696</v>
+        <v>619605</v>
       </c>
       <c r="R40" t="n">
-        <v>7013344</v>
+        <v>7013212</v>
       </c>
       <c r="S40" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4978,22 +4978,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133039510</v>
+        <v>133039534</v>
       </c>
       <c r="B41" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>619605</v>
+        <v>619647</v>
       </c>
       <c r="R41" t="n">
-        <v>7013212</v>
+        <v>7013315</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5097,48 +5097,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133039534</v>
+        <v>133041161</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>97995</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>619647</v>
+        <v>619696</v>
       </c>
       <c r="R42" t="n">
-        <v>7013315</v>
+        <v>7013344</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5192,12 +5192,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5953,48 +5953,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133041130</v>
+        <v>133039514</v>
       </c>
       <c r="B50" t="n">
-        <v>79333</v>
+        <v>97995</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>619658</v>
+        <v>619610</v>
       </c>
       <c r="R50" t="n">
-        <v>7013169</v>
+        <v>7013231</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6048,12 +6048,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6175,48 +6175,51 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133039514</v>
+        <v>133039530</v>
       </c>
       <c r="B52" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>619610</v>
+        <v>619558</v>
       </c>
       <c r="R52" t="n">
-        <v>7013231</v>
+        <v>7013324</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6245,7 +6248,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6255,7 +6258,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6264,6 +6267,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6282,10 +6286,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133039530</v>
+        <v>133041130</v>
       </c>
       <c r="B53" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6293,40 +6297,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>619558</v>
+        <v>619658</v>
       </c>
       <c r="R53" t="n">
-        <v>7013324</v>
+        <v>7013169</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6355,7 +6356,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6365,7 +6366,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6374,19 +6375,18 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6834,10 +6834,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133039540</v>
+        <v>133041139</v>
       </c>
       <c r="B58" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6845,45 +6845,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>619839</v>
+        <v>619607</v>
       </c>
       <c r="R58" t="n">
-        <v>7013377</v>
+        <v>7013209</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6912,7 +6904,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6922,12 +6914,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,12 +6929,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7061,10 +7048,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133041139</v>
+        <v>133039540</v>
       </c>
       <c r="B60" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7072,37 +7059,45 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>619607</v>
+        <v>619839</v>
       </c>
       <c r="R60" t="n">
-        <v>7013209</v>
+        <v>7013377</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7131,7 +7126,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7141,7 +7136,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7156,12 +7156,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7831,48 +7831,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133039547</v>
+        <v>133041127</v>
       </c>
       <c r="B67" t="n">
-        <v>92378</v>
+        <v>79333</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>619754</v>
+        <v>619662</v>
       </c>
       <c r="R67" t="n">
-        <v>7013242</v>
+        <v>7013101</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7926,44 +7926,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133039542</v>
+        <v>133039547</v>
       </c>
       <c r="B68" t="n">
-        <v>79333</v>
+        <v>92378</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7973,10 +7973,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>619802</v>
+        <v>619754</v>
       </c>
       <c r="R68" t="n">
-        <v>7013443</v>
+        <v>7013242</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8045,10 +8045,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133039494</v>
+        <v>133039542</v>
       </c>
       <c r="B69" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8056,37 +8056,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>619655</v>
+        <v>619802</v>
       </c>
       <c r="R69" t="n">
-        <v>7013115</v>
+        <v>7013443</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -8118,7 +8115,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8128,7 +8125,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8137,7 +8134,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8156,10 +8152,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133039502</v>
+        <v>133039494</v>
       </c>
       <c r="B70" t="n">
-        <v>91932</v>
+        <v>92217</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8167,34 +8163,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>619662</v>
+        <v>619655</v>
       </c>
       <c r="R70" t="n">
-        <v>7013170</v>
+        <v>7013115</v>
       </c>
       <c r="S70" t="n">
         <v>3</v>
@@ -8226,7 +8225,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8236,7 +8235,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8245,6 +8244,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133039548</v>
+        <v>133039491</v>
       </c>
       <c r="B71" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8274,37 +8274,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>619671</v>
+        <v>619664</v>
       </c>
       <c r="R71" t="n">
-        <v>7013153</v>
+        <v>7013113</v>
       </c>
       <c r="S71" t="n">
         <v>3</v>
@@ -8336,7 +8333,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8346,12 +8343,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Växandes på gammal sälg</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8360,24 +8352,8 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8394,10 +8370,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133041127</v>
+        <v>133039502</v>
       </c>
       <c r="B72" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8405,37 +8381,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
         <v>619662</v>
       </c>
       <c r="R72" t="n">
-        <v>7013101</v>
+        <v>7013170</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8464,7 +8440,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8474,7 +8450,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8489,22 +8465,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133039491</v>
+        <v>133039548</v>
       </c>
       <c r="B73" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8512,34 +8488,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>619664</v>
+        <v>619671</v>
       </c>
       <c r="R73" t="n">
-        <v>7013113</v>
+        <v>7013153</v>
       </c>
       <c r="S73" t="n">
         <v>3</v>
@@ -8571,7 +8550,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8581,7 +8560,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Växandes på gammal sälg</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8590,8 +8574,24 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8937,42 +8937,46 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133039500</v>
+        <v>133039513</v>
       </c>
       <c r="B77" t="n">
-        <v>57136</v>
+        <v>99130</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8980,10 +8984,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>619677</v>
+        <v>619602</v>
       </c>
       <c r="R77" t="n">
-        <v>7013160</v>
+        <v>7013238</v>
       </c>
       <c r="S77" t="n">
         <v>3</v>
@@ -9015,7 +9019,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9025,7 +9029,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9034,6 +9038,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9052,46 +9057,42 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133039513</v>
+        <v>133039500</v>
       </c>
       <c r="B78" t="n">
-        <v>99130</v>
+        <v>57136</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9099,10 +9100,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>619602</v>
+        <v>619677</v>
       </c>
       <c r="R78" t="n">
-        <v>7013238</v>
+        <v>7013160</v>
       </c>
       <c r="S78" t="n">
         <v>3</v>
@@ -9134,7 +9135,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9144,7 +9145,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9153,7 +9154,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9279,37 +9279,46 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133039527</v>
+        <v>133039528</v>
       </c>
       <c r="B80" t="n">
-        <v>91932</v>
+        <v>99130</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9317,10 +9326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>619516</v>
+        <v>619496</v>
       </c>
       <c r="R80" t="n">
-        <v>7013323</v>
+        <v>7013322</v>
       </c>
       <c r="S80" t="n">
         <v>2</v>
@@ -9352,7 +9361,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9362,7 +9371,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9390,10 +9399,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133039532</v>
+        <v>133039527</v>
       </c>
       <c r="B81" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9401,37 +9410,40 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>619594</v>
+        <v>619516</v>
       </c>
       <c r="R81" t="n">
-        <v>7013273</v>
+        <v>7013323</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9460,7 +9472,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9470,7 +9482,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9479,6 +9491,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9497,60 +9510,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133039528</v>
+        <v>133039532</v>
       </c>
       <c r="B82" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>619496</v>
+        <v>619594</v>
       </c>
       <c r="R82" t="n">
-        <v>7013322</v>
+        <v>7013273</v>
       </c>
       <c r="S82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9579,7 +9580,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9589,7 +9590,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9598,7 +9599,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3426-2026 artfynd.xlsx
+++ b/artfynd/A 3426-2026 artfynd.xlsx
@@ -1025,45 +1025,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133039525</v>
+        <v>133039495</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619539</v>
+        <v>619649</v>
       </c>
       <c r="R5" t="n">
-        <v>7013311</v>
+        <v>7013130</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1095,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,37 +1140,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133039512</v>
+        <v>133039492</v>
       </c>
       <c r="B6" t="n">
-        <v>92378</v>
+        <v>57955</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619598</v>
+        <v>619666</v>
       </c>
       <c r="R6" t="n">
-        <v>7013213</v>
+        <v>7013114</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,12 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bilden visar rynkskinn, rosenticka och ullticka på en granlåga.</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1237,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1248,48 +1255,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133041169</v>
+        <v>133039525</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619745</v>
+        <v>619539</v>
       </c>
       <c r="R7" t="n">
-        <v>7013238</v>
+        <v>7013311</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,54 +1350,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133039495</v>
+        <v>133039512</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>92378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619649</v>
+        <v>619598</v>
       </c>
       <c r="R8" t="n">
-        <v>7013130</v>
+        <v>7013213</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1445,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bilden visar rynkskinn, rosenticka och ullticka på en granlåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,6 +1459,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1470,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133039492</v>
+        <v>133041169</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,45 +1489,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619666</v>
+        <v>619745</v>
       </c>
       <c r="R9" t="n">
-        <v>7013114</v>
+        <v>7013238</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,12 +1573,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -3327,46 +3327,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133039550</v>
+        <v>133039541</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>57136</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3374,10 +3370,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619673</v>
+        <v>619819</v>
       </c>
       <c r="R26" t="n">
-        <v>7013115</v>
+        <v>7013478</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3409,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3419,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3428,7 +3424,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3440,14 +3435,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133039541</v>
+        <v>133039536</v>
       </c>
       <c r="B27" t="n">
         <v>57136</v>
@@ -3480,7 +3475,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3490,10 +3485,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>619819</v>
+        <v>619674</v>
       </c>
       <c r="R27" t="n">
-        <v>7013478</v>
+        <v>7013329</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3525,7 +3520,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3535,7 +3530,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3562,42 +3557,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133039536</v>
+        <v>133039550</v>
       </c>
       <c r="B28" t="n">
-        <v>57136</v>
+        <v>99130</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3605,10 +3604,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>619674</v>
+        <v>619673</v>
       </c>
       <c r="R28" t="n">
-        <v>7013329</v>
+        <v>7013115</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3640,7 +3639,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3650,7 +3649,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3659,6 +3658,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3670,17 +3670,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133041170</v>
+        <v>133039521</v>
       </c>
       <c r="B29" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3688,45 +3688,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>619669</v>
+        <v>619582</v>
       </c>
       <c r="R29" t="n">
-        <v>7013158</v>
+        <v>7013292</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3755,7 +3747,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3765,7 +3757,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3780,19 +3772,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133039529</v>
+        <v>133039496</v>
       </c>
       <c r="B30" t="n">
         <v>79333</v>
@@ -3821,19 +3813,22 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>619498</v>
+        <v>619651</v>
       </c>
       <c r="R30" t="n">
-        <v>7013345</v>
+        <v>7013134</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3862,7 +3857,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3872,7 +3867,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3881,6 +3876,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3899,10 +3895,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133039521</v>
+        <v>133039544</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3910,21 +3906,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3934,13 +3930,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>619582</v>
+        <v>619872</v>
       </c>
       <c r="R31" t="n">
-        <v>7013292</v>
+        <v>7013296</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3969,7 +3965,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3979,7 +3975,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4006,51 +4002,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133039496</v>
+        <v>133041154</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>619651</v>
+        <v>619554</v>
       </c>
       <c r="R32" t="n">
-        <v>7013134</v>
+        <v>7013316</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4079,7 +4072,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4089,7 +4082,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4098,29 +4091,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133039544</v>
+        <v>133041170</v>
       </c>
       <c r="B33" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4128,37 +4120,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>619872</v>
+        <v>619669</v>
       </c>
       <c r="R33" t="n">
-        <v>7013296</v>
+        <v>7013158</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4212,60 +4212,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133041154</v>
+        <v>133039529</v>
       </c>
       <c r="B34" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>619554</v>
+        <v>619498</v>
       </c>
       <c r="R34" t="n">
-        <v>7013316</v>
+        <v>7013345</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4319,12 +4319,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4763,57 +4763,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133039520</v>
+        <v>133039510</v>
       </c>
       <c r="B39" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>619585</v>
+        <v>619605</v>
       </c>
       <c r="R39" t="n">
-        <v>7013257</v>
+        <v>7013212</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4845,7 +4833,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,7 +4843,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4864,7 +4852,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4883,10 +4870,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133039510</v>
+        <v>133039534</v>
       </c>
       <c r="B40" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4894,21 +4881,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4918,10 +4905,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>619605</v>
+        <v>619647</v>
       </c>
       <c r="R40" t="n">
-        <v>7013212</v>
+        <v>7013315</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4953,7 +4940,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4963,7 +4950,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4990,45 +4977,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133039534</v>
+        <v>133039520</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>619647</v>
+        <v>619585</v>
       </c>
       <c r="R41" t="n">
-        <v>7013315</v>
+        <v>7013257</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -5060,7 +5059,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5070,7 +5069,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5079,6 +5078,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133039519</v>
+        <v>133039549</v>
       </c>
       <c r="B43" t="n">
-        <v>91881</v>
+        <v>80473</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>619592</v>
+        <v>619663</v>
       </c>
       <c r="R43" t="n">
-        <v>7013241</v>
+        <v>7013148</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5311,7 +5311,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133039535</v>
+        <v>133039519</v>
       </c>
       <c r="B44" t="n">
         <v>91881</v>
@@ -5346,13 +5346,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>619667</v>
+        <v>619592</v>
       </c>
       <c r="R44" t="n">
-        <v>7013336</v>
+        <v>7013241</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5418,7 +5418,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133039507</v>
+        <v>133039535</v>
       </c>
       <c r="B45" t="n">
         <v>91881</v>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>619673</v>
+        <v>619667</v>
       </c>
       <c r="R45" t="n">
-        <v>7013196</v>
+        <v>7013336</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5525,48 +5525,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133041147</v>
+        <v>133039507</v>
       </c>
       <c r="B46" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>619523</v>
+        <v>619673</v>
       </c>
       <c r="R46" t="n">
-        <v>7013308</v>
+        <v>7013196</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5620,44 +5620,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133041143</v>
+        <v>133041147</v>
       </c>
       <c r="B47" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>619558</v>
+        <v>619523</v>
       </c>
       <c r="R47" t="n">
-        <v>7013293</v>
+        <v>7013308</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5739,48 +5739,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133039537</v>
+        <v>133041143</v>
       </c>
       <c r="B48" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>619664</v>
+        <v>619558</v>
       </c>
       <c r="R48" t="n">
-        <v>7013327</v>
+        <v>7013293</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5834,44 +5834,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133039549</v>
+        <v>133039537</v>
       </c>
       <c r="B49" t="n">
-        <v>80473</v>
+        <v>91918</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5881,13 +5881,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>619663</v>
+        <v>619664</v>
       </c>
       <c r="R49" t="n">
-        <v>7013148</v>
+        <v>7013327</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5953,48 +5953,56 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133039514</v>
+        <v>133041138</v>
       </c>
       <c r="B50" t="n">
-        <v>97995</v>
+        <v>57955</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>619610</v>
+        <v>619593</v>
       </c>
       <c r="R50" t="n">
-        <v>7013231</v>
+        <v>7013220</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6023,7 +6031,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6033,7 +6041,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6048,68 +6056,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133041138</v>
+        <v>133039514</v>
       </c>
       <c r="B51" t="n">
-        <v>57955</v>
+        <v>97995</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>619593</v>
+        <v>619610</v>
       </c>
       <c r="R51" t="n">
-        <v>7013220</v>
+        <v>7013231</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6163,12 +6163,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -7510,10 +7510,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133039506</v>
+        <v>133039548</v>
       </c>
       <c r="B64" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7521,37 +7521,40 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>619674</v>
+        <v>619671</v>
       </c>
       <c r="R64" t="n">
-        <v>7013194</v>
+        <v>7013153</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7580,7 +7583,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7590,7 +7593,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Växandes på gammal sälg</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7599,8 +7607,24 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7617,7 +7641,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133039505</v>
+        <v>133039491</v>
       </c>
       <c r="B65" t="n">
         <v>79333</v>
@@ -7652,13 +7676,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>619683</v>
+        <v>619664</v>
       </c>
       <c r="R65" t="n">
-        <v>7013204</v>
+        <v>7013113</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7687,7 +7711,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7697,7 +7721,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7724,48 +7748,56 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133039504</v>
+        <v>133041135</v>
       </c>
       <c r="B66" t="n">
-        <v>91881</v>
+        <v>56522</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>619679</v>
+        <v>619690</v>
       </c>
       <c r="R66" t="n">
-        <v>7013155</v>
+        <v>7013194</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7794,7 +7826,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7804,7 +7836,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7819,22 +7851,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133041127</v>
+        <v>133039506</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7842,37 +7874,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>619662</v>
+        <v>619674</v>
       </c>
       <c r="R67" t="n">
-        <v>7013101</v>
+        <v>7013194</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7901,7 +7933,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7911,7 +7943,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7926,44 +7958,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133039547</v>
+        <v>133039505</v>
       </c>
       <c r="B68" t="n">
-        <v>92378</v>
+        <v>79333</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7973,13 +8005,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>619754</v>
+        <v>619683</v>
       </c>
       <c r="R68" t="n">
-        <v>7013242</v>
+        <v>7013204</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8008,7 +8040,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8018,7 +8050,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8045,32 +8077,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133039542</v>
+        <v>133039504</v>
       </c>
       <c r="B69" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8080,13 +8112,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>619802</v>
+        <v>619679</v>
       </c>
       <c r="R69" t="n">
-        <v>7013443</v>
+        <v>7013155</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8115,7 +8147,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8125,7 +8157,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8152,10 +8184,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133039494</v>
+        <v>133041127</v>
       </c>
       <c r="B70" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8163,40 +8195,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>619655</v>
+        <v>619662</v>
       </c>
       <c r="R70" t="n">
-        <v>7013115</v>
+        <v>7013101</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8225,7 +8254,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8235,7 +8264,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8244,51 +8273,50 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133039491</v>
+        <v>133039547</v>
       </c>
       <c r="B71" t="n">
-        <v>79333</v>
+        <v>92378</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8298,10 +8326,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>619664</v>
+        <v>619754</v>
       </c>
       <c r="R71" t="n">
-        <v>7013113</v>
+        <v>7013242</v>
       </c>
       <c r="S71" t="n">
         <v>3</v>
@@ -8333,7 +8361,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8343,7 +8371,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8370,10 +8398,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133039502</v>
+        <v>133039542</v>
       </c>
       <c r="B72" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8381,21 +8409,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8405,10 +8433,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>619662</v>
+        <v>619802</v>
       </c>
       <c r="R72" t="n">
-        <v>7013170</v>
+        <v>7013443</v>
       </c>
       <c r="S72" t="n">
         <v>3</v>
@@ -8440,7 +8468,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8450,7 +8478,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8477,10 +8505,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133039548</v>
+        <v>133039494</v>
       </c>
       <c r="B73" t="n">
-        <v>80438</v>
+        <v>92217</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8488,21 +8516,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8515,10 +8543,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>619671</v>
+        <v>619655</v>
       </c>
       <c r="R73" t="n">
-        <v>7013153</v>
+        <v>7013115</v>
       </c>
       <c r="S73" t="n">
         <v>3</v>
@@ -8550,7 +8578,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8560,12 +8588,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Växandes på gammal sälg</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8577,21 +8600,6 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8608,10 +8616,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133041135</v>
+        <v>133039502</v>
       </c>
       <c r="B74" t="n">
-        <v>56522</v>
+        <v>91932</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8619,45 +8627,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>206004</v>
+        <v>1204</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>619690</v>
+        <v>619662</v>
       </c>
       <c r="R74" t="n">
-        <v>7013194</v>
+        <v>7013170</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8711,22 +8711,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133041149</v>
+        <v>133039500</v>
       </c>
       <c r="B75" t="n">
-        <v>91918</v>
+        <v>57136</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8734,37 +8734,45 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Källopptjärnen, Ång</t>
+          <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>619498</v>
+        <v>619677</v>
       </c>
       <c r="R75" t="n">
-        <v>7013329</v>
+        <v>7013160</v>
       </c>
       <c r="S75" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8793,7 +8801,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8803,7 +8811,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8818,57 +8826,69 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133039497</v>
+        <v>133039513</v>
       </c>
       <c r="B76" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>619647</v>
+        <v>619602</v>
       </c>
       <c r="R76" t="n">
-        <v>7013144</v>
+        <v>7013238</v>
       </c>
       <c r="S76" t="n">
         <v>3</v>
@@ -8900,7 +8920,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8910,7 +8930,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8919,6 +8939,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8937,60 +8958,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133039513</v>
+        <v>133041149</v>
       </c>
       <c r="B77" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Källoppstjärnen, Ång</t>
+          <t>Källopptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>619602</v>
+        <v>619498</v>
       </c>
       <c r="R77" t="n">
-        <v>7013238</v>
+        <v>7013329</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9019,7 +9028,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9029,7 +9038,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9038,72 +9047,63 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133039500</v>
+        <v>133039497</v>
       </c>
       <c r="B78" t="n">
-        <v>57136</v>
+        <v>91881</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>619677</v>
+        <v>619647</v>
       </c>
       <c r="R78" t="n">
-        <v>7013160</v>
+        <v>7013144</v>
       </c>
       <c r="S78" t="n">
         <v>3</v>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9279,46 +9279,37 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133039528</v>
+        <v>133039527</v>
       </c>
       <c r="B80" t="n">
-        <v>99130</v>
+        <v>91932</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9326,10 +9317,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>619496</v>
+        <v>619516</v>
       </c>
       <c r="R80" t="n">
-        <v>7013322</v>
+        <v>7013323</v>
       </c>
       <c r="S80" t="n">
         <v>2</v>
@@ -9361,7 +9352,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9371,7 +9362,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9399,10 +9390,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133039527</v>
+        <v>133039532</v>
       </c>
       <c r="B81" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9410,40 +9401,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>619516</v>
+        <v>619594</v>
       </c>
       <c r="R81" t="n">
-        <v>7013323</v>
+        <v>7013273</v>
       </c>
       <c r="S81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9472,7 +9460,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9482,7 +9470,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9491,7 +9479,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9510,48 +9497,60 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133039532</v>
+        <v>133039528</v>
       </c>
       <c r="B82" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Källoppstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>619594</v>
+        <v>619496</v>
       </c>
       <c r="R82" t="n">
-        <v>7013273</v>
+        <v>7013322</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9580,7 +9579,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9590,7 +9589,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9599,6 +9598,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
